--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 2/ОБЩИНА АКСАКОВО % 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,22 +55,16 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>ТУБА</t>
@@ -85,52 +76,19 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
-  </si>
-  <si>
-    <t>4 Л. AHTИФPИЗ ГOTOB ЗA УПOTPEБA (-37°C)</t>
-  </si>
-  <si>
-    <t>0.25L BRAKE FLUID SUPER NEW</t>
-  </si>
-  <si>
-    <t>10 L. EKO ADBLUE</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>14:44:00</t>
-  </si>
-  <si>
-    <t>09:56:00</t>
-  </si>
-  <si>
-    <t>09:21:00</t>
-  </si>
-  <si>
-    <t>13:39:00</t>
-  </si>
-  <si>
-    <t>11:42:00</t>
-  </si>
-  <si>
-    <t>3235887434 3235887434</t>
-  </si>
-  <si>
-    <t>3236250976 3236250976</t>
-  </si>
-  <si>
-    <t>3236853470 3236853470</t>
-  </si>
-  <si>
-    <t>3236912009 3236912009</t>
-  </si>
-  <si>
-    <t>3237168974 3237168974</t>
+    <t>4 Л. AHTИФPИЗ ЛOHГ Л</t>
+  </si>
+  <si>
+    <t>4 Л. AHTИФPИЗ ГOTOB</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>14:52</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 2</t>
@@ -551,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -560,17 +518,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -610,469 +567,282 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
       </c>
       <c r="F2">
         <v>120</v>
       </c>
-      <c r="G2" t="s">
-        <v>27</v>
+      <c r="G2" s="1">
+        <v>1.58</v>
       </c>
       <c r="H2" s="1">
-        <v>1.52</v>
+        <v>189.6</v>
       </c>
       <c r="I2" s="1">
-        <v>182.4</v>
+        <v>1.61</v>
       </c>
       <c r="J2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>186</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
+        <v>193.2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
+        <v>145692</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>26.79</v>
+      </c>
+      <c r="H3" s="1">
+        <v>53.58</v>
+      </c>
+      <c r="I3" s="1">
+        <v>26.79</v>
+      </c>
+      <c r="J3" s="1">
+        <v>53.58</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="M3">
+        <v>252854</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>80.04000000000001</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="I3" s="1">
-        <v>121.661</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="K3" s="1">
-        <v>124.062</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1">
+        <v>15.89</v>
+      </c>
+      <c r="H4" s="1">
+        <v>31.78</v>
+      </c>
+      <c r="I4" s="1">
+        <v>15.89</v>
+      </c>
+      <c r="J4" s="1">
+        <v>31.78</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="1">
-        <v>9.49</v>
-      </c>
-      <c r="I4" s="1">
-        <v>37.96</v>
-      </c>
-      <c r="J4" s="1">
-        <v>9.49</v>
-      </c>
-      <c r="K4" s="1">
-        <v>37.96</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>252854</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5">
+        <v>120.07</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H5" s="1">
+        <v>193.313</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J5" s="1">
+        <v>196.915</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>254672</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="6">
+        <v>240.07</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.59501</v>
+      </c>
+      <c r="E10" s="6">
+        <v>382.91</v>
+      </c>
+      <c r="F10" s="6">
+        <v>390.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="6">
+        <v>2</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>15.89</v>
+      </c>
+      <c r="E11" s="6">
+        <v>31.78</v>
+      </c>
+      <c r="F11" s="6">
+        <v>31.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5">
+      <c r="B12" s="6">
+        <v>2</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
+        <v>26.79</v>
+      </c>
+      <c r="E12" s="6">
+        <v>53.58</v>
+      </c>
+      <c r="F12" s="6">
+        <v>53.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="10">
+        <v>244.07</v>
+      </c>
+      <c r="C13" s="11">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="1">
-        <v>15.89</v>
-      </c>
-      <c r="I5" s="1">
-        <v>63.56</v>
-      </c>
-      <c r="J5" s="1">
-        <v>15.89</v>
-      </c>
-      <c r="K5" s="1">
-        <v>63.56</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>120</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="I6" s="1">
-        <v>184.8</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="K6" s="1">
-        <v>188.4</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="1">
-        <v>3.06</v>
-      </c>
-      <c r="I7" s="1">
-        <v>15.3</v>
-      </c>
-      <c r="J7" s="1">
-        <v>3.06</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15.3</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1">
-        <v>25.49</v>
-      </c>
-      <c r="I8" s="1">
-        <v>127.45</v>
-      </c>
-      <c r="J8" s="1">
-        <v>25.49</v>
-      </c>
-      <c r="K8" s="1">
-        <v>127.45</v>
-      </c>
-      <c r="L8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="6">
-        <v>320.04</v>
-      </c>
-      <c r="C13" s="7">
-        <v>3</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.5275</v>
-      </c>
-      <c r="E13" s="6">
-        <v>488.86</v>
-      </c>
-      <c r="F13" s="6">
-        <v>498.46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="6">
-        <v>5</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8">
-        <v>3.06</v>
-      </c>
-      <c r="E14" s="6">
-        <v>15.3</v>
-      </c>
-      <c r="F14" s="6">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="6">
-        <v>5</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8">
-        <v>25.49</v>
-      </c>
-      <c r="E15" s="6">
-        <v>127.45</v>
-      </c>
-      <c r="F15" s="6">
-        <v>127.45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="6">
-        <v>4</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8">
-        <v>15.89</v>
-      </c>
-      <c r="E16" s="6">
-        <v>63.56</v>
-      </c>
-      <c r="F16" s="6">
-        <v>63.56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="6">
-        <v>4</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8">
-        <v>9.49</v>
-      </c>
-      <c r="E17" s="6">
-        <v>37.96</v>
-      </c>
-      <c r="F17" s="6">
-        <v>37.96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="10">
-        <v>338.04</v>
-      </c>
-      <c r="C18" s="11">
-        <v>7</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="10">
-        <v>733.13</v>
-      </c>
-      <c r="F18" s="10">
-        <v>742.73</v>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>468.27</v>
+      </c>
+      <c r="F13" s="10">
+        <v>475.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
